--- a/out/CLB4_BFR_sample.xlsx
+++ b/out/CLB4_BFR_sample.xlsx
@@ -139,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,6 +191,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1060,120 +1066,215 @@
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>ELECNX/COMMS MAINT SHOP  (Loading driver: Comm Maint billets)</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>SECTION 1 - ADMINISTRATIVE SPACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Personnel Category</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>SF / Person</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>GSF</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Primary loading row</t>
-        </is>
-      </c>
-      <c r="V8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="13" t="n">
-        <v>99</v>
-      </c>
-      <c r="AB8" s="14">
-        <f>V8*Y8*1.0</f>
-        <v/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="V9" s="13" t="inlineStr"/>
-      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Comm Maint Officers</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y9" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="AB9" s="14">
-        <f>V9*Y9*1.0</f>
+        <f>V9*Y9</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="12" t="inlineStr"/>
-      <c r="V10" s="13" t="inlineStr"/>
-      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Comm Maint Enlisted</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y10" s="13" t="n">
+        <v>30</v>
+      </c>
       <c r="AB10" s="14">
-        <f>V10*Y10*1.0</f>
+        <f>V10*Y10</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="12" t="inlineStr"/>
-      <c r="V11" s="13" t="inlineStr"/>
-      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Administrative Subtotal</t>
+        </is>
+      </c>
       <c r="AB11" s="14">
-        <f>V11*Y11*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="12" t="inlineStr"/>
-      <c r="V12" s="13" t="inlineStr"/>
-      <c r="Y12" s="13" t="inlineStr"/>
-      <c r="AB12" s="14">
-        <f>V12*Y12*1.0</f>
-        <v/>
-      </c>
-    </row>
+        <f>SUM(AB9:AB10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1"/>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="12" t="inlineStr"/>
-      <c r="V13" s="13" t="inlineStr"/>
-      <c r="Y13" s="13" t="inlineStr"/>
-      <c r="AB13" s="14">
-        <f>V13*Y13*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1"/>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>SECTION 2 - MAINTENANCE BAYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>Vehicle Category</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>SF / Bay</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+    </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Subtotal NSF</t>
-        </is>
-      </c>
-      <c r="AB15" s="14">
-        <f>SUM(AB8:AF13)</f>
-        <v/>
-      </c>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Comm vehicles (radio shelters)</t>
+        </is>
+      </c>
+      <c r="V15" s="21" t="n">
+        <v>420</v>
+      </c>
+      <c r="Y15" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Net to Gross multiplier (NTG = 1.0)</t>
-        </is>
-      </c>
-      <c r="AB16" s="14">
-        <f>AB15*1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
+      <c r="A16" s="12" t="inlineStr"/>
+      <c r="V16" s="21" t="inlineStr"/>
+      <c r="Y16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="12" t="inlineStr"/>
+      <c r="V17" s="21" t="inlineStr"/>
+      <c r="Y17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Total Self-Propelled Vehicles | CEILING(total / 15) bays</t>
+        </is>
+      </c>
+      <c r="V18" s="21" t="inlineStr"/>
+      <c r="Y18" s="14">
+        <f>SUM(Y15:Y17)</f>
+        <v/>
+      </c>
+      <c r="AB18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Maintenance Bays (CEILING bays per 15 vehicles)</t>
+        </is>
+      </c>
+      <c r="V19" s="21" t="n">
+        <v>420</v>
+      </c>
+      <c r="Y19" s="14">
+        <f>CEILING(Y18/15,1)</f>
+        <v/>
+      </c>
+      <c r="AB19" s="14">
+        <f>V19*Y19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Maintenance Bays Subtotal</t>
+        </is>
+      </c>
+      <c r="AB20" s="14">
+        <f>AB19</f>
+        <v/>
+      </c>
+    </row>
     <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL SPACE REQUIREMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Total NSF (Administrative + Maintenance Bays)</t>
+        </is>
+      </c>
+      <c r="AB23" s="14">
+        <f>AB11+AB20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>NTG Factor = 1.33, Required GSF = ROUNDUP(NSF * NTG, 0)</t>
+        </is>
+      </c>
+      <c r="V24" s="13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Y24" s="21" t="inlineStr"/>
+      <c r="AB24" s="14">
+        <f>ROUNDUP(AB23*V24,0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -1193,7 +1294,7 @@
         </is>
       </c>
       <c r="H37" s="17">
-        <f>AB16</f>
+        <f>AB24</f>
         <v/>
       </c>
       <c r="O37" s="18" t="inlineStr">
@@ -1204,58 +1305,75 @@
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="69">
     <mergeCell ref="V10:X10"/>
-    <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="A13:AF13"/>
+    <mergeCell ref="Y14:AA14"/>
     <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="A16:U16"/>
     <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="AB18:AF18"/>
     <mergeCell ref="V9:X9"/>
-    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="V24:X24"/>
+    <mergeCell ref="AB24:AF24"/>
+    <mergeCell ref="AB20:AF20"/>
     <mergeCell ref="H37:K37"/>
+    <mergeCell ref="AB14:AF14"/>
+    <mergeCell ref="Y17:AA17"/>
     <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="Y7:AA7"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="A18:U18"/>
+    <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="R3:AC3"/>
-    <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="AB16:AF16"/>
-    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="Y18:AA18"/>
+    <mergeCell ref="A14:U14"/>
     <mergeCell ref="AB9:AF9"/>
-    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A7:AF7"/>
+    <mergeCell ref="A17:U17"/>
+    <mergeCell ref="A23:AA23"/>
     <mergeCell ref="A8:U8"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="V16:X16"/>
     <mergeCell ref="C5:L5"/>
-    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="V19:X19"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="A20:AA20"/>
+    <mergeCell ref="A19:U19"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="A10:U10"/>
-    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="V18:X18"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
-    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="V17:X17"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB23:AF23"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="A37:G37"/>
+    <mergeCell ref="AB17:AF17"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="AB13:AF13"/>
-    <mergeCell ref="AB7:AF7"/>
-    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A24:U24"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="A15:U15"/>
     <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="Y15:AA15"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB19:AF19"/>
+    <mergeCell ref="A22:AF22"/>
     <mergeCell ref="AB10:AF10"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="A11:AA11"/>
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0"/>
@@ -1404,120 +1522,215 @@
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>FLD MAINT SHOP(ELEC/COMMS)  (Loading driver: Field Maint billets)</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>SECTION 1 - ADMINISTRATIVE SPACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Personnel Category</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>SF / Person</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>GSF</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Primary loading row</t>
-        </is>
-      </c>
-      <c r="V8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="13" t="n">
-        <v>99</v>
-      </c>
-      <c r="AB8" s="14">
-        <f>V8*Y8*1.0</f>
-        <v/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="V9" s="13" t="inlineStr"/>
-      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Field Maint Officers</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y9" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="AB9" s="14">
-        <f>V9*Y9*1.0</f>
+        <f>V9*Y9</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="12" t="inlineStr"/>
-      <c r="V10" s="13" t="inlineStr"/>
-      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Field Maint Enlisted</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y10" s="13" t="n">
+        <v>33</v>
+      </c>
       <c r="AB10" s="14">
-        <f>V10*Y10*1.0</f>
+        <f>V10*Y10</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="12" t="inlineStr"/>
-      <c r="V11" s="13" t="inlineStr"/>
-      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Administrative Subtotal</t>
+        </is>
+      </c>
       <c r="AB11" s="14">
-        <f>V11*Y11*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="12" t="inlineStr"/>
-      <c r="V12" s="13" t="inlineStr"/>
-      <c r="Y12" s="13" t="inlineStr"/>
-      <c r="AB12" s="14">
-        <f>V12*Y12*1.0</f>
-        <v/>
-      </c>
-    </row>
+        <f>SUM(AB9:AB10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1"/>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="12" t="inlineStr"/>
-      <c r="V13" s="13" t="inlineStr"/>
-      <c r="Y13" s="13" t="inlineStr"/>
-      <c r="AB13" s="14">
-        <f>V13*Y13*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1"/>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>SECTION 2 - MAINTENANCE BAYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>Vehicle Category</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>SF / Bay</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+    </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Subtotal NSF</t>
-        </is>
-      </c>
-      <c r="AB15" s="14">
-        <f>SUM(AB8:AF13)</f>
-        <v/>
-      </c>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Field maintenance vehicles</t>
+        </is>
+      </c>
+      <c r="V15" s="21" t="n">
+        <v>420</v>
+      </c>
+      <c r="Y15" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Net to Gross multiplier (NTG = 1.0)</t>
-        </is>
-      </c>
-      <c r="AB16" s="14">
-        <f>AB15*1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
+      <c r="A16" s="12" t="inlineStr"/>
+      <c r="V16" s="21" t="inlineStr"/>
+      <c r="Y16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="12" t="inlineStr"/>
+      <c r="V17" s="21" t="inlineStr"/>
+      <c r="Y17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Total Self-Propelled Vehicles | CEILING(total / 15) bays</t>
+        </is>
+      </c>
+      <c r="V18" s="21" t="inlineStr"/>
+      <c r="Y18" s="14">
+        <f>SUM(Y15:Y17)</f>
+        <v/>
+      </c>
+      <c r="AB18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Maintenance Bays (CEILING bays per 15 vehicles)</t>
+        </is>
+      </c>
+      <c r="V19" s="21" t="n">
+        <v>420</v>
+      </c>
+      <c r="Y19" s="14">
+        <f>CEILING(Y18/15,1)</f>
+        <v/>
+      </c>
+      <c r="AB19" s="14">
+        <f>V19*Y19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Maintenance Bays Subtotal</t>
+        </is>
+      </c>
+      <c r="AB20" s="14">
+        <f>AB19</f>
+        <v/>
+      </c>
+    </row>
     <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL SPACE REQUIREMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Total NSF (Administrative + Maintenance Bays)</t>
+        </is>
+      </c>
+      <c r="AB23" s="14">
+        <f>AB11+AB20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>NTG Factor = 1.33, Required GSF = ROUNDUP(NSF * NTG, 0)</t>
+        </is>
+      </c>
+      <c r="V24" s="13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Y24" s="21" t="inlineStr"/>
+      <c r="AB24" s="14">
+        <f>ROUNDUP(AB23*V24,0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -1537,7 +1750,7 @@
         </is>
       </c>
       <c r="H37" s="17">
-        <f>AB16</f>
+        <f>AB24</f>
         <v/>
       </c>
       <c r="O37" s="18" t="inlineStr">
@@ -1548,58 +1761,75 @@
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="69">
     <mergeCell ref="V10:X10"/>
-    <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="A13:AF13"/>
+    <mergeCell ref="Y14:AA14"/>
     <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="A16:U16"/>
     <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="AB18:AF18"/>
     <mergeCell ref="V9:X9"/>
-    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="V24:X24"/>
+    <mergeCell ref="AB24:AF24"/>
+    <mergeCell ref="AB20:AF20"/>
     <mergeCell ref="H37:K37"/>
+    <mergeCell ref="AB14:AF14"/>
+    <mergeCell ref="Y17:AA17"/>
     <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="Y7:AA7"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="A18:U18"/>
+    <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="R3:AC3"/>
-    <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="AB16:AF16"/>
-    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="Y18:AA18"/>
+    <mergeCell ref="A14:U14"/>
     <mergeCell ref="AB9:AF9"/>
-    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A7:AF7"/>
+    <mergeCell ref="A17:U17"/>
+    <mergeCell ref="A23:AA23"/>
     <mergeCell ref="A8:U8"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="V16:X16"/>
     <mergeCell ref="C5:L5"/>
-    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="V19:X19"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="A20:AA20"/>
+    <mergeCell ref="A19:U19"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="A10:U10"/>
-    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="V18:X18"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
-    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="V17:X17"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB23:AF23"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="A37:G37"/>
+    <mergeCell ref="AB17:AF17"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="AB13:AF13"/>
-    <mergeCell ref="AB7:AF7"/>
-    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A24:U24"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="A15:U15"/>
     <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="Y15:AA15"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB19:AF19"/>
+    <mergeCell ref="A22:AF22"/>
     <mergeCell ref="AB10:AF10"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="A11:AA11"/>
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0"/>
@@ -1750,7 +1980,7 @@
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>STG AIR/GRD ORG UTS MARCOR  (Loading driver: Org storage)</t>
+          <t>STG AIR/GRD ORG UTS MARCOR (Loading driver: Storage personnel)</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -1776,13 +2006,13 @@
         </is>
       </c>
       <c r="V8" s="13" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="Y8" s="13" t="n">
         <v>84</v>
       </c>
       <c r="AB8" s="14">
-        <f>V8*Y8*1.0</f>
+        <f>V8*Y8*1.33</f>
         <v/>
       </c>
     </row>
@@ -1791,7 +2021,7 @@
       <c r="V9" s="13" t="inlineStr"/>
       <c r="Y9" s="13" t="inlineStr"/>
       <c r="AB9" s="14">
-        <f>V9*Y9*1.0</f>
+        <f>V9*Y9*1.33</f>
         <v/>
       </c>
     </row>
@@ -1800,7 +2030,7 @@
       <c r="V10" s="13" t="inlineStr"/>
       <c r="Y10" s="13" t="inlineStr"/>
       <c r="AB10" s="14">
-        <f>V10*Y10*1.0</f>
+        <f>V10*Y10*1.33</f>
         <v/>
       </c>
     </row>
@@ -1809,7 +2039,7 @@
       <c r="V11" s="13" t="inlineStr"/>
       <c r="Y11" s="13" t="inlineStr"/>
       <c r="AB11" s="14">
-        <f>V11*Y11*1.0</f>
+        <f>V11*Y11*1.33</f>
         <v/>
       </c>
     </row>
@@ -1818,7 +2048,7 @@
       <c r="V12" s="13" t="inlineStr"/>
       <c r="Y12" s="13" t="inlineStr"/>
       <c r="AB12" s="14">
-        <f>V12*Y12*1.0</f>
+        <f>V12*Y12*1.33</f>
         <v/>
       </c>
     </row>
@@ -1827,7 +2057,7 @@
       <c r="V13" s="13" t="inlineStr"/>
       <c r="Y13" s="13" t="inlineStr"/>
       <c r="AB13" s="14">
-        <f>V13*Y13*1.0</f>
+        <f>V13*Y13*1.33</f>
         <v/>
       </c>
     </row>
@@ -1846,7 +2076,7 @@
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Net to Gross multiplier (NTG = 1.0)</t>
+          <t>Net to Gross multiplier (NTG = 1.33)</t>
         </is>
       </c>
       <c r="AB16" s="14">
@@ -2094,7 +2324,7 @@
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>OPEN STORAGE AREA  (Loading driver: Open storage)</t>
+          <t>OPEN STORAGE AREA (Loading driver: Open storage area)</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -2224,7 +2454,7 @@
           <t>TOTAL REQUIREMENT:</t>
         </is>
       </c>
-      <c r="H37" s="20">
+      <c r="H37" s="22">
         <f>AB16</f>
         <v/>
       </c>
@@ -2660,12 +2890,12 @@
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>ARMORY  (Loading driver: PN_MIL)</t>
+          <t>Sensitive Item Category (Primary Items, all four companies)</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>GSF / Item</t>
         </is>
       </c>
       <c r="Y7" s="4" t="inlineStr">
@@ -2682,62 +2912,102 @@
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Primary loading row</t>
+          <t>Night Vision Devices (AN/PVS-14, AN/PVS-31D)</t>
         </is>
       </c>
       <c r="V8" s="13" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="Y8" s="13" t="n">
-        <v>310</v>
+        <v>237</v>
       </c>
       <c r="AB8" s="14">
-        <f>V8*Y8*1.0</f>
+        <f>V8*Y8</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="V9" s="13" t="inlineStr"/>
-      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Machine Guns (M240B, MK19 MOD 3)</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y9" s="13" t="n">
+        <v>14</v>
+      </c>
       <c r="AB9" s="14">
-        <f>V9*Y9*1.0</f>
+        <f>V9*Y9</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="12" t="inlineStr"/>
-      <c r="V10" s="13" t="inlineStr"/>
-      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Rifles, Carbines, and Shotguns</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y10" s="13" t="n">
+        <v>19</v>
+      </c>
       <c r="AB10" s="14">
-        <f>V10*Y10*1.0</f>
+        <f>V10*Y10</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="12" t="inlineStr"/>
-      <c r="V11" s="13" t="inlineStr"/>
-      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Grenade Launchers (M320A1)</t>
+        </is>
+      </c>
+      <c r="V11" s="13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y11" s="13" t="n">
+        <v>4</v>
+      </c>
       <c r="AB11" s="14">
-        <f>V11*Y11*1.0</f>
+        <f>V11*Y11</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="12" t="inlineStr"/>
-      <c r="V12" s="13" t="inlineStr"/>
-      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Thermal Sights (AN/PAS-13D)</t>
+        </is>
+      </c>
+      <c r="V12" s="13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y12" s="13" t="n">
+        <v>4</v>
+      </c>
       <c r="AB12" s="14">
-        <f>V12*Y12*1.0</f>
+        <f>V12*Y12</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="12" t="inlineStr"/>
-      <c r="V13" s="13" t="inlineStr"/>
-      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Other Sensitive Items (Optics, Accessories, Spares)</t>
+        </is>
+      </c>
+      <c r="V13" s="13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y13" s="13" t="n">
+        <v>52</v>
+      </c>
       <c r="AB13" s="14">
-        <f>V13*Y13*1.0</f>
+        <f>V13*Y13</f>
         <v/>
       </c>
     </row>
@@ -2745,22 +3015,22 @@
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Subtotal NSF</t>
+          <t>Total Sensitive Items, Total NSF</t>
         </is>
       </c>
       <c r="AB15" s="14">
-        <f>SUM(AB8:AF13)</f>
+        <f>SUM(AB8:AB13)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Net to Gross multiplier (NTG = 1.0)</t>
+          <t>Required GSF = ROUNDUP(Total NSF, 0)</t>
         </is>
       </c>
       <c r="AB16" s="14">
-        <f>AB15*1</f>
+        <f>ROUNDUP(AB15,0)</f>
         <v/>
       </c>
     </row>
@@ -3002,120 +3272,227 @@
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>AUTO ORGANIZATIONAL SHOP  (Loading driver: Vehicle count)</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>SECTION 1 - ADMINISTRATIVE SPACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Personnel Category</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>SF / Person</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>GSF</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Primary loading row</t>
-        </is>
-      </c>
-      <c r="V8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="13" t="n">
-        <v>84</v>
-      </c>
-      <c r="AB8" s="14">
-        <f>V8*Y8*1.2</f>
-        <v/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="V9" s="13" t="inlineStr"/>
-      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Officers, Private Offices (Platoon Commanders)</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y9" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="AB9" s="14">
-        <f>V9*Y9*1.2</f>
+        <f>V9*Y9</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="12" t="inlineStr"/>
-      <c r="V10" s="13" t="inlineStr"/>
-      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>SNCOs and Staff, Cubicles</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y10" s="13" t="n">
+        <v>11</v>
+      </c>
       <c r="AB10" s="14">
-        <f>V10*Y10*1.2</f>
+        <f>V10*Y10</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="12" t="inlineStr"/>
-      <c r="V11" s="13" t="inlineStr"/>
-      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Administrative Subtotal</t>
+        </is>
+      </c>
       <c r="AB11" s="14">
-        <f>V11*Y11*1.2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="12" t="inlineStr"/>
-      <c r="V12" s="13" t="inlineStr"/>
-      <c r="Y12" s="13" t="inlineStr"/>
-      <c r="AB12" s="14">
-        <f>V12*Y12*1.2</f>
-        <v/>
-      </c>
-    </row>
+        <f>SUM(AB9:AB10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1"/>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="12" t="inlineStr"/>
-      <c r="V13" s="13" t="inlineStr"/>
-      <c r="Y13" s="13" t="inlineStr"/>
-      <c r="AB13" s="14">
-        <f>V13*Y13*1.2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1"/>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>SECTION 2 - MAINTENANCE BAYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>Vehicle Category</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>SF / Bay</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+    </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Subtotal NSF</t>
-        </is>
-      </c>
-      <c r="AB15" s="14">
-        <f>SUM(AB8:AF13)</f>
-        <v/>
-      </c>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Light Utility Vehicles (JLTV-class M1280, M1279)</t>
+        </is>
+      </c>
+      <c r="V15" s="21" t="n">
+        <v>420</v>
+      </c>
+      <c r="Y15" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="AB15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Net to Gross multiplier (NTG = 1.2)</t>
-        </is>
-      </c>
-      <c r="AB16" s="14">
-        <f>AB15*1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Medium / Heavy Cargo (AMK23A1, AMK27A1)</t>
+        </is>
+      </c>
+      <c r="V16" s="21" t="n">
+        <v>420</v>
+      </c>
+      <c r="Y16" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Wrecker / Recovery (AMK36)</t>
+        </is>
+      </c>
+      <c r="V17" s="21" t="n">
+        <v>420</v>
+      </c>
+      <c r="Y17" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Total Self-Propelled Vehicles | CEILING(total / 30) bays</t>
+        </is>
+      </c>
+      <c r="V18" s="21" t="inlineStr"/>
+      <c r="Y18" s="14">
+        <f>SUM(Y15:Y17)</f>
+        <v/>
+      </c>
+      <c r="AB18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Maintenance Bays (CEILING bays per 30 vehicles)</t>
+        </is>
+      </c>
+      <c r="V19" s="21" t="n">
+        <v>420</v>
+      </c>
+      <c r="Y19" s="14">
+        <f>CEILING(Y18/30,1)</f>
+        <v/>
+      </c>
+      <c r="AB19" s="14">
+        <f>V19*Y19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Maintenance Bays Subtotal</t>
+        </is>
+      </c>
+      <c r="AB20" s="14">
+        <f>AB19</f>
+        <v/>
+      </c>
+    </row>
     <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL SPACE REQUIREMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Total NSF (Administrative + Maintenance Bays)</t>
+        </is>
+      </c>
+      <c r="AB23" s="14">
+        <f>AB11+AB20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>NTG Factor = 1.33, Required GSF = ROUNDUP(NSF * NTG, 0)</t>
+        </is>
+      </c>
+      <c r="V24" s="13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Y24" s="21" t="inlineStr"/>
+      <c r="AB24" s="14">
+        <f>ROUNDUP(AB23*V24,0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -3135,7 +3512,7 @@
         </is>
       </c>
       <c r="H37" s="17">
-        <f>AB16</f>
+        <f>AB24</f>
         <v/>
       </c>
       <c r="O37" s="18" t="inlineStr">
@@ -3146,58 +3523,75 @@
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="69">
     <mergeCell ref="V10:X10"/>
-    <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="A13:AF13"/>
+    <mergeCell ref="Y14:AA14"/>
     <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="A16:U16"/>
     <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="AB18:AF18"/>
     <mergeCell ref="V9:X9"/>
-    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="V24:X24"/>
+    <mergeCell ref="AB24:AF24"/>
+    <mergeCell ref="AB20:AF20"/>
     <mergeCell ref="H37:K37"/>
+    <mergeCell ref="AB14:AF14"/>
+    <mergeCell ref="Y17:AA17"/>
     <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="Y7:AA7"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="A18:U18"/>
+    <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="R3:AC3"/>
-    <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="AB16:AF16"/>
-    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="Y18:AA18"/>
+    <mergeCell ref="A14:U14"/>
     <mergeCell ref="AB9:AF9"/>
-    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A7:AF7"/>
+    <mergeCell ref="A17:U17"/>
+    <mergeCell ref="A23:AA23"/>
     <mergeCell ref="A8:U8"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="V16:X16"/>
     <mergeCell ref="C5:L5"/>
-    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="V19:X19"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="A20:AA20"/>
+    <mergeCell ref="A19:U19"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="A10:U10"/>
-    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="V18:X18"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
-    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="V17:X17"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB23:AF23"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="A37:G37"/>
+    <mergeCell ref="AB17:AF17"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="AB13:AF13"/>
-    <mergeCell ref="AB7:AF7"/>
-    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A24:U24"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="A15:U15"/>
     <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="Y15:AA15"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB19:AF19"/>
+    <mergeCell ref="A22:AF22"/>
     <mergeCell ref="AB10:AF10"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="A11:AA11"/>
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0"/>
@@ -3348,7 +3742,7 @@
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>VEHICLE WASH PLATFORM  (Loading driver: Vehicle count)</t>
+          <t>VEHICLE WASH PLATFORM (Loading driver: Vehicle wash spaces)</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -3690,116 +4084,138 @@
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>BATTLN SQUADRN HQ (MARCOR)  (Loading driver: Admin billets)</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>GSF</t>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>BILLETS EXCLUDED FROM THIS CCN (require separate facility CCNs)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Primary loading row</t>
-        </is>
-      </c>
-      <c r="V8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="13" t="n">
-        <v>84</v>
-      </c>
-      <c r="AB8" s="14">
-        <f>V8*Y8*1.0</f>
-        <v/>
+          <t>Medical / BAS billets (34), medical facility CCN required</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="V9" s="13" t="inlineStr"/>
-      <c r="Y9" s="13" t="inlineStr"/>
-      <c r="AB9" s="14">
-        <f>V9*Y9*1.0</f>
-        <v/>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>EOD Section billets (13), EOD facility CCN required</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="12" t="inlineStr"/>
-      <c r="V10" s="13" t="inlineStr"/>
-      <c r="Y10" s="13" t="inlineStr"/>
-      <c r="AB10" s="14">
-        <f>V10*Y10*1.0</f>
-        <v/>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Specialist shop billets (99), maintenance shop CCN(s) required</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="12" t="inlineStr"/>
-      <c r="V11" s="13" t="inlineStr"/>
-      <c r="Y11" s="13" t="inlineStr"/>
-      <c r="AB11" s="14">
-        <f>V11*Y11*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="12" t="inlineStr"/>
-      <c r="V12" s="13" t="inlineStr"/>
-      <c r="Y12" s="13" t="inlineStr"/>
-      <c r="AB12" s="14">
-        <f>V12*Y12*1.0</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Ordnance repair billets (10), ordnance shop CCN required</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1"/>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="12" t="inlineStr"/>
-      <c r="V13" s="13" t="inlineStr"/>
-      <c r="Y13" s="13" t="inlineStr"/>
-      <c r="AB13" s="14">
-        <f>V13*Y13*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1"/>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE SPACE CALCULATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Space Type</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>SF / Person</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+    </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Subtotal NSF</t>
-        </is>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Private Offices (CO, XO, CSE, Chaplain, S-Staff Officers)</t>
+        </is>
+      </c>
+      <c r="V15" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y15" s="13" t="n">
+        <v>21</v>
       </c>
       <c r="AB15" s="14">
-        <f>SUM(AB8:AF13)</f>
+        <f>V15*Y15</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Net to Gross multiplier (NTG = 1.0)</t>
-        </is>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Cubicles (S-Staff NCOs, Company Admin, Supply, Ops)</t>
+        </is>
+      </c>
+      <c r="V16" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y16" s="13" t="n">
+        <v>63</v>
       </c>
       <c r="AB16" s="14">
-        <f>AB15*1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1"/>
+        <f>V16*Y16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Total NSF</t>
+        </is>
+      </c>
+      <c r="AB17" s="14">
+        <f>SUM(AB15:AB16)</f>
+        <v/>
+      </c>
+    </row>
     <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL SPACE REQUIREMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>NTG Factor = 1.33, Required GSF = ROUNDUP(NSF * NTG, 0)</t>
+        </is>
+      </c>
+      <c r="V20" s="13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Y20" s="21" t="inlineStr"/>
+      <c r="AB20" s="14">
+        <f>ROUNDUP(AB17*V20,0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -3823,7 +4239,7 @@
         </is>
       </c>
       <c r="H37" s="17">
-        <f>AB16</f>
+        <f>AB20</f>
         <v/>
       </c>
       <c r="O37" s="18" t="inlineStr">
@@ -3834,57 +4250,50 @@
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="52">
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="Y11:AA11"/>
+  <mergeCells count="45">
+    <mergeCell ref="A10:AF10"/>
+    <mergeCell ref="Y20:AA20"/>
     <mergeCell ref="Y4:AF4"/>
-    <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="A13:AF13"/>
+    <mergeCell ref="Y14:AA14"/>
+    <mergeCell ref="A16:U16"/>
+    <mergeCell ref="A19:AF19"/>
     <mergeCell ref="AB15:AF15"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="A16:AA16"/>
     <mergeCell ref="H37:K37"/>
+    <mergeCell ref="AB20:AF20"/>
+    <mergeCell ref="A9:AF9"/>
+    <mergeCell ref="AB14:AF14"/>
     <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="Y7:AA7"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="A11:AF11"/>
+    <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
     <mergeCell ref="R3:AC3"/>
-    <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="AB16:AF16"/>
-    <mergeCell ref="Y12:AA12"/>
-    <mergeCell ref="AB9:AF9"/>
-    <mergeCell ref="V7:X7"/>
-    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A14:U14"/>
+    <mergeCell ref="A7:AF7"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="V16:X16"/>
     <mergeCell ref="C5:L5"/>
-    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="A17:AA17"/>
+    <mergeCell ref="A20:U20"/>
     <mergeCell ref="R4:X4"/>
-    <mergeCell ref="AB11:AF11"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="Y8:AA8"/>
-    <mergeCell ref="A10:U10"/>
-    <mergeCell ref="V12:X12"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
-    <mergeCell ref="A13:U13"/>
     <mergeCell ref="M3:Q3"/>
-    <mergeCell ref="A9:U9"/>
-    <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="A37:G37"/>
+    <mergeCell ref="AB17:AF17"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="AB13:AF13"/>
-    <mergeCell ref="AB7:AF7"/>
-    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="A15:U15"/>
     <mergeCell ref="A1:AF2"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="A11:U11"/>
-    <mergeCell ref="AB10:AF10"/>
-    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="A8:AF8"/>
+    <mergeCell ref="V20:X20"/>
     <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
@@ -4036,7 +4445,7 @@
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>OPRTNL VEHICLE LAYDWN AREA  (Loading driver: Vehicle count)</t>
+          <t>OPRTNL VEHICLE LAYDWN AREA (Loading driver: Vehicle laydown areas)</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -4166,7 +4575,7 @@
           <t>TOTAL REQUIREMENT:</t>
         </is>
       </c>
-      <c r="H37" s="20">
+      <c r="H37" s="22">
         <f>AB16</f>
         <v/>
       </c>
@@ -4378,112 +4787,104 @@
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>MARINE CORPS EOD PLATOON  (Loading driver: EOD billets)</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE SPACE CALCULATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>EOD Personnel Space</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>SF / Person</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>GSF</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Primary loading row</t>
-        </is>
-      </c>
-      <c r="V8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB8" s="14">
-        <f>V8*Y8*1.0</f>
-        <v/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="V9" s="13" t="inlineStr"/>
-      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>EOD Officers, Private Offices</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y9" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="AB9" s="14">
-        <f>V9*Y9*1.0</f>
+        <f>V9*Y9</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="12" t="inlineStr"/>
-      <c r="V10" s="13" t="inlineStr"/>
-      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>EOD Enlisted, Workspace</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y10" s="13" t="n">
+        <v>11</v>
+      </c>
       <c r="AB10" s="14">
-        <f>V10*Y10*1.0</f>
+        <f>V10*Y10</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="12" t="inlineStr"/>
-      <c r="V11" s="13" t="inlineStr"/>
-      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Total NSF</t>
+        </is>
+      </c>
       <c r="AB11" s="14">
-        <f>V11*Y11*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="12" t="inlineStr"/>
-      <c r="V12" s="13" t="inlineStr"/>
-      <c r="Y12" s="13" t="inlineStr"/>
-      <c r="AB12" s="14">
-        <f>V12*Y12*1.0</f>
-        <v/>
-      </c>
-    </row>
+        <f>SUM(AB9:AB10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1"/>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="12" t="inlineStr"/>
-      <c r="V13" s="13" t="inlineStr"/>
-      <c r="Y13" s="13" t="inlineStr"/>
-      <c r="AB13" s="14">
-        <f>V13*Y13*1.0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Subtotal NSF</t>
-        </is>
-      </c>
-      <c r="AB15" s="14">
-        <f>SUM(AB8:AF13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Net to Gross multiplier (NTG = 1.0)</t>
-        </is>
-      </c>
-      <c r="AB16" s="14">
-        <f>AB15*1</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL SPACE REQUIREMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>NTG Factor = 1.33, Required GSF = ROUNDUP(NSF * NTG, 0)</t>
+        </is>
+      </c>
+      <c r="V14" s="13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Y14" s="21" t="inlineStr"/>
+      <c r="AB14" s="14">
+        <f>ROUNDUP(AB11*V14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
@@ -4511,7 +4912,7 @@
         </is>
       </c>
       <c r="H37" s="17">
-        <f>AB16</f>
+        <f>AB14</f>
         <v/>
       </c>
       <c r="O37" s="18" t="inlineStr">
@@ -4522,58 +4923,46 @@
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="40">
     <mergeCell ref="V10:X10"/>
-    <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="A13:AF13"/>
+    <mergeCell ref="Y14:AA14"/>
     <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="A7:U7"/>
-    <mergeCell ref="AB15:AF15"/>
     <mergeCell ref="V9:X9"/>
-    <mergeCell ref="A16:AA16"/>
     <mergeCell ref="H37:K37"/>
+    <mergeCell ref="AB14:AF14"/>
     <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="Y7:AA7"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="R3:AC3"/>
-    <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
     <mergeCell ref="F4:L4"/>
-    <mergeCell ref="AB16:AF16"/>
-    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="A14:U14"/>
     <mergeCell ref="AB9:AF9"/>
-    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A7:AF7"/>
     <mergeCell ref="A8:U8"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="C5:L5"/>
-    <mergeCell ref="AB12:AF12"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="A10:U10"/>
-    <mergeCell ref="V12:X12"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
-    <mergeCell ref="A13:U13"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="AB13:AF13"/>
-    <mergeCell ref="AB7:AF7"/>
-    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="V14:X14"/>
     <mergeCell ref="A1:AF2"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="A11:U11"/>
     <mergeCell ref="AB10:AF10"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="A11:AA11"/>
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0"/>

--- a/out/CLB4_BFR_sample.xlsx
+++ b/out/CLB4_BFR_sample.xlsx
@@ -108,7 +108,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -135,11 +135,55 @@
         <color rgb="00000000"/>
       </top>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,6 +235,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -940,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -1073,7 +1123,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Personnel Category</t>
         </is>
@@ -1148,7 +1198,7 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Vehicle Category</t>
         </is>
@@ -1175,29 +1225,29 @@
           <t>Comm vehicles (radio shelters)</t>
         </is>
       </c>
-      <c r="V15" s="21" t="n">
+      <c r="V15" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y15" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="AB15" s="21" t="inlineStr"/>
+      <c r="AB15" s="25" t="inlineStr"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="12" t="inlineStr"/>
-      <c r="V16" s="21" t="inlineStr"/>
+      <c r="V16" s="25" t="inlineStr"/>
       <c r="Y16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AB16" s="21" t="inlineStr"/>
+      <c r="AB16" s="25" t="inlineStr"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="12" t="inlineStr"/>
-      <c r="V17" s="21" t="inlineStr"/>
+      <c r="V17" s="25" t="inlineStr"/>
       <c r="Y17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" s="21" t="inlineStr"/>
+      <c r="AB17" s="25" t="inlineStr"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -1205,12 +1255,12 @@
           <t>Total Self-Propelled Vehicles | CEILING(total / 15) bays</t>
         </is>
       </c>
-      <c r="V18" s="21" t="inlineStr"/>
+      <c r="V18" s="25" t="inlineStr"/>
       <c r="Y18" s="14">
         <f>SUM(Y15:Y17)</f>
         <v/>
       </c>
-      <c r="AB18" s="21" t="inlineStr"/>
+      <c r="AB18" s="25" t="inlineStr"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -1218,7 +1268,7 @@
           <t>Maintenance Bays (CEILING bays per 15 vehicles)</t>
         </is>
       </c>
-      <c r="V19" s="21" t="n">
+      <c r="V19" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y19" s="14">
@@ -1269,7 +1319,7 @@
       <c r="V24" s="13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Y24" s="21" t="inlineStr"/>
+      <c r="Y24" s="25" t="inlineStr"/>
       <c r="AB24" s="14">
         <f>ROUNDUP(AB23*V24,0)</f>
         <v/>
@@ -1304,8 +1354,86 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 200 Series; version date 2025-05-16</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_200series_05_16_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [195]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 21710-1: Electronics maintenance shops at Naval and Marine Corps activities</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="75">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y4:AF4"/>
     <mergeCell ref="A13:AF13"/>
@@ -1320,13 +1448,16 @@
     <mergeCell ref="AB24:AF24"/>
     <mergeCell ref="AB20:AF20"/>
     <mergeCell ref="H37:K37"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="AB14:AF14"/>
     <mergeCell ref="Y17:AA17"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="V15:X15"/>
     <mergeCell ref="A18:U18"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="A6:AF6"/>
@@ -1354,6 +1485,8 @@
     <mergeCell ref="V18:X18"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
@@ -1368,6 +1501,7 @@
     <mergeCell ref="A15:U15"/>
     <mergeCell ref="A1:AF2"/>
     <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="AB19:AF19"/>
@@ -1396,7 +1530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -1529,7 +1663,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Personnel Category</t>
         </is>
@@ -1604,7 +1738,7 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Vehicle Category</t>
         </is>
@@ -1631,29 +1765,29 @@
           <t>Field maintenance vehicles</t>
         </is>
       </c>
-      <c r="V15" s="21" t="n">
+      <c r="V15" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y15" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="AB15" s="21" t="inlineStr"/>
+      <c r="AB15" s="25" t="inlineStr"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="12" t="inlineStr"/>
-      <c r="V16" s="21" t="inlineStr"/>
+      <c r="V16" s="25" t="inlineStr"/>
       <c r="Y16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AB16" s="21" t="inlineStr"/>
+      <c r="AB16" s="25" t="inlineStr"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="12" t="inlineStr"/>
-      <c r="V17" s="21" t="inlineStr"/>
+      <c r="V17" s="25" t="inlineStr"/>
       <c r="Y17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" s="21" t="inlineStr"/>
+      <c r="AB17" s="25" t="inlineStr"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -1661,12 +1795,12 @@
           <t>Total Self-Propelled Vehicles | CEILING(total / 15) bays</t>
         </is>
       </c>
-      <c r="V18" s="21" t="inlineStr"/>
+      <c r="V18" s="25" t="inlineStr"/>
       <c r="Y18" s="14">
         <f>SUM(Y15:Y17)</f>
         <v/>
       </c>
-      <c r="AB18" s="21" t="inlineStr"/>
+      <c r="AB18" s="25" t="inlineStr"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -1674,7 +1808,7 @@
           <t>Maintenance Bays (CEILING bays per 15 vehicles)</t>
         </is>
       </c>
-      <c r="V19" s="21" t="n">
+      <c r="V19" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y19" s="14">
@@ -1725,7 +1859,7 @@
       <c r="V24" s="13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Y24" s="21" t="inlineStr"/>
+      <c r="Y24" s="25" t="inlineStr"/>
       <c r="AB24" s="14">
         <f>ROUNDUP(AB23*V24,0)</f>
         <v/>
@@ -1760,8 +1894,99 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 200 Series; version date 2025-05-16</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_200series_05_16_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [196]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 21730-1: This field maintenance shop provides specialized work areas for</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>UoM source: CCN_VOCABULARY.json (Appendix A 2019-06-27); Series PDF heading omitted UoM, ratifier should verify against current Series text</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="76">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y4:AF4"/>
     <mergeCell ref="A13:AF13"/>
@@ -1776,13 +2001,16 @@
     <mergeCell ref="AB24:AF24"/>
     <mergeCell ref="AB20:AF20"/>
     <mergeCell ref="H37:K37"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="AB14:AF14"/>
     <mergeCell ref="Y17:AA17"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="V15:X15"/>
     <mergeCell ref="A18:U18"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="A6:AF6"/>
@@ -1798,6 +2026,7 @@
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="V16:X16"/>
     <mergeCell ref="C5:L5"/>
+    <mergeCell ref="B46:H46"/>
     <mergeCell ref="V19:X19"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
@@ -1810,6 +2039,8 @@
     <mergeCell ref="V18:X18"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
@@ -1824,6 +2055,7 @@
     <mergeCell ref="A15:U15"/>
     <mergeCell ref="A1:AF2"/>
     <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="AB19:AF19"/>
@@ -1852,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -2121,11 +2353,64 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 400 (Maintenance &amp; Production; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 441 12 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="56">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="Y10:AA10"/>
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
@@ -2137,6 +2422,7 @@
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
@@ -2151,6 +2437,7 @@
     <mergeCell ref="AB12:AF12"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
@@ -2159,6 +2446,7 @@
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -2196,7 +2484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -2454,7 +2742,7 @@
           <t>TOTAL REQUIREMENT:</t>
         </is>
       </c>
-      <c r="H37" s="22">
+      <c r="H37" s="26">
         <f>AB16</f>
         <v/>
       </c>
@@ -2465,11 +2753,64 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 400 (Maintenance &amp; Production; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 451 10 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="56">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="Y10:AA10"/>
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
@@ -2481,6 +2822,7 @@
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
@@ -2495,6 +2837,7 @@
     <mergeCell ref="AB12:AF12"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
@@ -2503,6 +2846,7 @@
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -2762,7 +3106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -3071,11 +3415,77 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 100 Series; version date 2026-02-11</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_100series_02_11_2026.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [205]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Table 14345-1 (Armory); loading driver: Installation Military Strength</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="57">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="Y10:AA10"/>
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
@@ -3087,6 +3497,7 @@
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
@@ -3101,6 +3512,7 @@
     <mergeCell ref="AB12:AF12"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
@@ -3109,6 +3521,7 @@
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -3118,6 +3531,7 @@
     <mergeCell ref="AB7:AF7"/>
     <mergeCell ref="A15:AA15"/>
     <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="A11:U11"/>
@@ -3146,7 +3560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -3279,7 +3693,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Personnel Category</t>
         </is>
@@ -3354,7 +3768,7 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Vehicle Category</t>
         </is>
@@ -3381,13 +3795,13 @@
           <t>Light Utility Vehicles (JLTV-class M1280, M1279)</t>
         </is>
       </c>
-      <c r="V15" s="21" t="n">
+      <c r="V15" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y15" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="AB15" s="21" t="inlineStr"/>
+      <c r="AB15" s="25" t="inlineStr"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -3395,13 +3809,13 @@
           <t>Medium / Heavy Cargo (AMK23A1, AMK27A1)</t>
         </is>
       </c>
-      <c r="V16" s="21" t="n">
+      <c r="V16" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y16" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="AB16" s="21" t="inlineStr"/>
+      <c r="AB16" s="25" t="inlineStr"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -3409,13 +3823,13 @@
           <t>Wrecker / Recovery (AMK36)</t>
         </is>
       </c>
-      <c r="V17" s="21" t="n">
+      <c r="V17" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y17" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="AB17" s="21" t="inlineStr"/>
+      <c r="AB17" s="25" t="inlineStr"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -3423,12 +3837,12 @@
           <t>Total Self-Propelled Vehicles | CEILING(total / 30) bays</t>
         </is>
       </c>
-      <c r="V18" s="21" t="inlineStr"/>
+      <c r="V18" s="25" t="inlineStr"/>
       <c r="Y18" s="14">
         <f>SUM(Y15:Y17)</f>
         <v/>
       </c>
-      <c r="AB18" s="21" t="inlineStr"/>
+      <c r="AB18" s="25" t="inlineStr"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -3436,7 +3850,7 @@
           <t>Maintenance Bays (CEILING bays per 30 vehicles)</t>
         </is>
       </c>
-      <c r="V19" s="21" t="n">
+      <c r="V19" s="25" t="n">
         <v>420</v>
       </c>
       <c r="Y19" s="14">
@@ -3487,7 +3901,7 @@
       <c r="V24" s="13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Y24" s="21" t="inlineStr"/>
+      <c r="Y24" s="25" t="inlineStr"/>
       <c r="AB24" s="14">
         <f>ROUNDUP(AB23*V24,0)</f>
         <v/>
@@ -3522,8 +3936,86 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 200 Series; version date 2025-05-16</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_200series_05_16_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [188]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 3 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 21451-1: This facility provides work areas for Fleet Marine Force (FMF) units to</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="75">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y4:AF4"/>
     <mergeCell ref="A13:AF13"/>
@@ -3538,13 +4030,16 @@
     <mergeCell ref="AB24:AF24"/>
     <mergeCell ref="AB20:AF20"/>
     <mergeCell ref="H37:K37"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="AB14:AF14"/>
     <mergeCell ref="Y17:AA17"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="V15:X15"/>
     <mergeCell ref="A18:U18"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="A6:AF6"/>
@@ -3572,6 +4067,8 @@
     <mergeCell ref="V18:X18"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
@@ -3586,6 +4083,7 @@
     <mergeCell ref="A15:U15"/>
     <mergeCell ref="A1:AF2"/>
     <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="AB19:AF19"/>
@@ -3614,7 +4112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -3883,11 +4381,90 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 200 Series; version date 2025-05-16</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_200series_05_16_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [188]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 21455-1: REQUIREMENTS. Vehicle wash platforms equipped with hose</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="58">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="Y10:AA10"/>
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
@@ -3896,9 +4473,11 @@
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
@@ -3913,6 +4492,7 @@
     <mergeCell ref="AB12:AF12"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
@@ -3921,6 +4501,7 @@
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -3930,6 +4511,7 @@
     <mergeCell ref="AB7:AF7"/>
     <mergeCell ref="A15:AA15"/>
     <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="A11:U11"/>
@@ -3958,7 +4540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -4210,7 +4792,7 @@
       <c r="V20" s="13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Y20" s="21" t="inlineStr"/>
+      <c r="Y20" s="25" t="inlineStr"/>
       <c r="AB20" s="14">
         <f>ROUNDUP(AB17*V20,0)</f>
         <v/>
@@ -4249,8 +4831,60 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 600 (Administrative; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 610 72 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="49">
     <mergeCell ref="A10:AF10"/>
     <mergeCell ref="Y20:AA20"/>
     <mergeCell ref="Y4:AF4"/>
@@ -4259,6 +4893,7 @@
     <mergeCell ref="A16:U16"/>
     <mergeCell ref="A19:AF19"/>
     <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="AB20:AF20"/>
     <mergeCell ref="A9:AF9"/>
@@ -4268,6 +4903,7 @@
     <mergeCell ref="A11:AF11"/>
     <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="A6:AF6"/>
     <mergeCell ref="F4:L4"/>
@@ -4280,10 +4916,12 @@
     <mergeCell ref="A17:AA17"/>
     <mergeCell ref="A20:U20"/>
     <mergeCell ref="R4:X4"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="AB17:AF17"/>
@@ -4317,7 +4955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -4575,7 +5213,7 @@
           <t>TOTAL REQUIREMENT:</t>
         </is>
       </c>
-      <c r="H37" s="22">
+      <c r="H37" s="26">
         <f>AB16</f>
         <v/>
       </c>
@@ -4586,11 +5224,103 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 100 Series; version date 2026-02-11</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_100series_02_11_2026.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [189, 190]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_190_table_1 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_190_table_2 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_190_table_3 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="59">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="Y10:AA10"/>
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
@@ -4599,9 +5329,11 @@
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
@@ -4612,10 +5344,12 @@
     <mergeCell ref="V7:X7"/>
     <mergeCell ref="A8:U8"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B46:H46"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="AB12:AF12"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
@@ -4624,6 +5358,7 @@
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -4633,6 +5368,7 @@
     <mergeCell ref="AB7:AF7"/>
     <mergeCell ref="A15:AA15"/>
     <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="A11:U11"/>
@@ -4661,7 +5397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -4877,7 +5613,7 @@
       <c r="V14" s="13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Y14" s="21" t="inlineStr"/>
+      <c r="Y14" s="25" t="inlineStr"/>
       <c r="AB14" s="14">
         <f>ROUNDUP(AB11*V14,0)</f>
         <v/>
@@ -4922,18 +5658,112 @@
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 100 Series; version date 2026-02-11</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_100series_02_11_2026.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [200, 201, 202, 203]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 24 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 14326-1: This facility is necessary for manning, equipping, and training for EOD</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>UoM source: CCN_VOCABULARY.json (Appendix A 2019-06-27); Series PDF heading omitted UoM, ratifier should verify against current Series text</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="47">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y4:AF4"/>
     <mergeCell ref="A13:AF13"/>
     <mergeCell ref="Y14:AA14"/>
     <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="V9:X9"/>
     <mergeCell ref="H37:K37"/>
     <mergeCell ref="AB14:AF14"/>
     <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="A6:AF6"/>
@@ -4943,15 +5773,18 @@
     <mergeCell ref="A7:AF7"/>
     <mergeCell ref="A8:U8"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B46:H46"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="F3:L3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="A10:U10"/>
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -4959,6 +5792,7 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="V14:X14"/>
     <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="AB10:AF10"/>

--- a/out/CLB4_BFR_sample.xlsx
+++ b/out/CLB4_BFR_sample.xlsx
@@ -20,6 +20,19 @@
     <sheet name="21730" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="44112" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="45110" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="53010" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="85210" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="85122" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="85121" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="87210" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="87250" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="87230" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="83143" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="83141" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="81160" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="88010" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="85235" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="85240" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'14345'!$A$1:$AF$37</definedName>
@@ -32,6 +45,19 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'21730'!$A$1:$AF$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'44112'!$A$1:$AF$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'45110'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'53010'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'85210'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'85122'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'85121'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'87210'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'87250'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'87230'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'83143'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'83141'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="22">'81160'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="23">'88010'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="24">'85235'!$A$1:$AF$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="25">'85240'!$A$1:$AF$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39,9 +65,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0\ &quot;GSF&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0\ &quot;GSY&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0\ &quot;LF&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0\ &quot;EA&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0\ &quot;KW&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0\ &quot;MI&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -183,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -249,6 +279,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -616,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF20"/>
+  <dimension ref="A1:AF33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -944,16 +986,289 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>530 10</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>DISP &amp; OUT PATIENT CLINIC</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="E19" s="6">
+        <f>'53010'!H37</f>
+        <v/>
+      </c>
+    </row>
     <row r="20">
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>852 10</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>PARKING AREA</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="E20" s="6">
+        <f>'85210'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>851 22</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>VEHICLE STAGING AREA</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="E21" s="6">
+        <f>'85122'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>851 21</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>VEH. PARK, UNSURFACED</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="E22" s="6">
+        <f>'85121'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>872 10</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>SECURTY/PERIMTR FENCE/WALL</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="E23" s="6">
+        <f>'87210'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>872 50</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>87250</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="E24" s="6">
+        <f>'87250'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>872 30</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>MECH SEC BARRICADE</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="E25" s="6">
+        <f>'87230'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>831 43</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>HAZ WASTE BLDG</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="E26" s="6">
+        <f>'83143'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>831 41</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>HAZARD WSTE STOR &amp; TRANSFR</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="E27" s="6">
+        <f>'83141'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>811 60</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>STANDBY GENERATOR PLANT</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="E28" s="6">
+        <f>'81160'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>880 10</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>FIRE ALARM COMM LINES</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="E29" s="6">
+        <f>'88010'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>852 35</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>OTHER PAVED AREA</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="E30" s="6">
+        <f>'85235'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>852 40</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>MISC OPEN STRG/LAYDOWN</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="E31" s="6">
+        <f>'85240'!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="9">
-        <f>SUM(E9:E18)</f>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="9">
+        <f>SUM(E9:E31)</f>
         <v/>
       </c>
     </row>
@@ -2084,6 +2399,1270 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>441 12</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>STG AIR/GRD ORG UTS MARCOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 441 12  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>STG AIR/GRD ORG UTS MARCOR (Loading driver: Storage personnel)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.33)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="17">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 400 Series; version date 2025-11-19</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_400series_11_19_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [46]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 44112-1: DESCRIPTION. This category code includes general purpose storage</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>451 10</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>OPEN STORAGE AREA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 451 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>OPEN STORAGE AREA (Loading driver: Open storage area)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="26">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 400 Series; version date 2025-11-19</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_400series_11_19_2025.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [50, 51]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 2 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 45110-1: DESCRIPTION. This category group consists of non-covered storage</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>530 10</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>DISP &amp; OUT PATIENT CLINIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 530 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE SPACE CALCULATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>BAS Personnel Space</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>SF / Person</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>NSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>BAS Medical Officers / IDC</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y9" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB9" s="14">
+        <f>V9*Y9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Hospital Corpsmen / Field Med Tech / Dental Asst</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y10" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB10" s="14">
+        <f>V10*Y10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Total NSF</t>
+        </is>
+      </c>
+      <c r="AB11" s="14">
+        <f>SUM(AB9:AB10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1"/>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL SPACE REQUIREMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>NTG Factor = 1.33, Required GSF = ROUNDUP(NSF * NTG, 0)</t>
+        </is>
+      </c>
+      <c r="V14" s="13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Y14" s="25" t="inlineStr"/>
+      <c r="AB14" s="14">
+        <f>ROUNDUP(AB11*V14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="17">
+        <f>AB14</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 500 Series; version date 2023-03-17</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_500series_03_17_2023.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [8]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 53010-1: GENERAL. Free Standing Clinic, outpatient clinic, which occupies a</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="46">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="A13:AF13"/>
+    <mergeCell ref="Y14:AA14"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="AB14:AF14"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="A14:U14"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="A7:AF7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="A11:AA11"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AF43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2188,7 +3767,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>441 12</t>
+          <t>852 10</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2198,21 +3777,21 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>STG AIR/GRD ORG UTS MARCOR</t>
+          <t>PARKING AREA</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28.5" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 441 12  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 852 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>STG AIR/GRD ORG UTS MARCOR (Loading driver: Storage personnel)</t>
+          <t>PARKING AREA (Loading driver: Organizational Vehicle Parking (count of CLB-4 motor pool vehicles); FAC 8521; cited factor 75 SY/vehicle for FMF Ground Units (50 SY/vehicle if &gt;50% are &lt;=18ft x 6.5ft); UoM=SY; user-supplied spec 2026-04-30 pending FC 2-000-05N Series 800 cross-check)</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -2227,7 +3806,7 @@
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>GSF</t>
+          <t>GSY</t>
         </is>
       </c>
     </row>
@@ -2238,13 +3817,13 @@
         </is>
       </c>
       <c r="V8" s="13" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Y8" s="13" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="AB8" s="14">
-        <f>V8*Y8*1.33</f>
+        <f>V8*Y8*1.0</f>
         <v/>
       </c>
     </row>
@@ -2253,7 +3832,7 @@
       <c r="V9" s="13" t="inlineStr"/>
       <c r="Y9" s="13" t="inlineStr"/>
       <c r="AB9" s="14">
-        <f>V9*Y9*1.33</f>
+        <f>V9*Y9*1.0</f>
         <v/>
       </c>
     </row>
@@ -2262,7 +3841,7 @@
       <c r="V10" s="13" t="inlineStr"/>
       <c r="Y10" s="13" t="inlineStr"/>
       <c r="AB10" s="14">
-        <f>V10*Y10*1.33</f>
+        <f>V10*Y10*1.0</f>
         <v/>
       </c>
     </row>
@@ -2271,7 +3850,7 @@
       <c r="V11" s="13" t="inlineStr"/>
       <c r="Y11" s="13" t="inlineStr"/>
       <c r="AB11" s="14">
-        <f>V11*Y11*1.33</f>
+        <f>V11*Y11*1.0</f>
         <v/>
       </c>
     </row>
@@ -2280,7 +3859,7 @@
       <c r="V12" s="13" t="inlineStr"/>
       <c r="Y12" s="13" t="inlineStr"/>
       <c r="AB12" s="14">
-        <f>V12*Y12*1.33</f>
+        <f>V12*Y12*1.0</f>
         <v/>
       </c>
     </row>
@@ -2289,7 +3868,7 @@
       <c r="V13" s="13" t="inlineStr"/>
       <c r="Y13" s="13" t="inlineStr"/>
       <c r="AB13" s="14">
-        <f>V13*Y13*1.33</f>
+        <f>V13*Y13*1.0</f>
         <v/>
       </c>
     </row>
@@ -2308,7 +3887,7 @@
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Net to Gross multiplier (NTG = 1.33)</t>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
         </is>
       </c>
       <c r="AB16" s="14">
@@ -2342,13 +3921,13 @@
           <t>TOTAL REQUIREMENT:</t>
         </is>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="26">
         <f>AB16</f>
         <v/>
       </c>
       <c r="O37" s="18" t="inlineStr">
         <is>
-          <t>GSF</t>
+          <t>GSY</t>
         </is>
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
@@ -2369,7 +3948,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>FC 2-000-05N citation: TBD pending Series 400 (Maintenance &amp; Production; not yet supplied)</t>
+          <t>FC 2-000-05N citation: TBD pending Series 800 (Utilities &amp; Ground; not yet supplied)</t>
         </is>
       </c>
       <c r="C41" s="21" t="n"/>
@@ -2382,7 +3961,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>CCN 441 12 not in supplied Series 100/200 PDFs</t>
+          <t>CCN 852 10 not in supplied Series 100/200 PDFs</t>
         </is>
       </c>
       <c r="C42" s="21" t="n"/>
@@ -2478,7 +4057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2588,7 +4167,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>451 10</t>
+          <t>851 22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2598,21 +4177,21 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>OPEN STORAGE AREA</t>
+          <t>VEHICLE STAGING AREA</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28.5" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 451 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 851 22  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>OPEN STORAGE AREA (Loading driver: Open storage area)</t>
+          <t>VEHICLE STAGING AREA (Loading driver: Vehicle Staging Area for mount-out operations (SY); FAC 8523; sized by mission scale not by parked-vehicle count; CLB-4 placeholder 5000 SY pending unit doctrine input)</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -2641,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="Y8" s="13" t="n">
-        <v>84</v>
+        <v>5000</v>
       </c>
       <c r="AB8" s="14">
         <f>V8*Y8*1.0</f>
@@ -2769,7 +4348,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>FC 2-000-05N citation: TBD pending Series 400 (Maintenance &amp; Production; not yet supplied)</t>
+          <t>FC 2-000-05N citation: TBD pending Series 800 (Utilities &amp; Ground; not yet supplied)</t>
         </is>
       </c>
       <c r="C41" s="21" t="n"/>
@@ -2782,7 +4361,1207 @@
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>CCN 451 10 not in supplied Series 100/200 PDFs</t>
+          <t>CCN 851 22 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>851 21</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>VEH. PARK, UNSURFACED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 851 21  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>VEH. PARK, UNSURFACED (Loading driver: Vehicular Parking Unsurfaced (SY); FAC 8522; calculated using 85210 criteria when used; CLB-4 sets to 0 because primary parking is paved per 85210)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="26">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 800 (Utilities &amp; Ground; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 851 21 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>872 10</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>SECURTY/PERIMTR FENCE/WALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 872 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>SECURTY/PERIMTR FENCE/WALL (Loading driver: Station Security and Perimeter Fencing (LF); FAC 8721; standard 7-ft chain link with 1.5-ft outriggers and 3 strands BB; min 50-150 ft from buildings/critical supplies; SRC I/II ammo fence per DoDM 5100.76 + UFC 4-022-03; CLB-4 placeholder 2000 LF pending compound perimeter survey)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="27">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>LF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 800 (Utilities &amp; Ground; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 872 10 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>872 50</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>87250</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 872 50  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>87250 (Loading driver: Entry Gate (LF); FAC 8721; CCN added Jan 2024; CLB-4 default 30 LF for 1-2 main gates pending site survey)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="28">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 800 (Utilities &amp; Ground; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 872 50 not in supplied Series 100/200 PDFs</t>
         </is>
       </c>
       <c r="C42" s="21" t="n"/>
@@ -2973,140 +5752,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:U4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>ROW</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>CCN</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>CCN Description</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>CCN 21451 Equipment Type</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>UIC</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>TAMCN Short</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>TAMCN</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Nomenclature</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>TAM Stat</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>U/I</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>Rdy</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>Ind Qty</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>Org Qty</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>Unit T/E</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>L, Ft</t>
-        </is>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>W, Ft</t>
-        </is>
-      </c>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>H, Ft</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>Volume Ea</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>Volume Total</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="84"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AF44"/>
+  <dimension ref="A1:AF43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -3210,7 +5862,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>143 45</t>
+          <t>872 30</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3220,26 +5872,26 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>ARMORY</t>
+          <t>MECH SEC BARRICADE</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28.5" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 143 45  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 872 30  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Sensitive Item Category (Primary Items, all four companies)</t>
+          <t>MECH SEC BARRICADE (Loading driver: Mechanical Security Barricade (EA); FAC 1458; drop arm barriers at gates; CLB-4 default 2 EA (one per gate))</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>GSF / Item</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="Y7" s="4" t="inlineStr">
@@ -3249,109 +5901,69 @@
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>GSF</t>
+          <t>EA</t>
         </is>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Night Vision Devices (AN/PVS-14, AN/PVS-31D)</t>
+          <t>Primary loading row</t>
         </is>
       </c>
       <c r="V8" s="13" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="Y8" s="13" t="n">
-        <v>237</v>
+        <v>2</v>
       </c>
       <c r="AB8" s="14">
-        <f>V8*Y8</f>
+        <f>V8*Y8*1.0</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Machine Guns (M240B, MK19 MOD 3)</t>
-        </is>
-      </c>
-      <c r="V9" s="13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Y9" s="13" t="n">
-        <v>14</v>
-      </c>
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
       <c r="AB9" s="14">
-        <f>V9*Y9</f>
+        <f>V9*Y9*1.0</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Rifles, Carbines, and Shotguns</t>
-        </is>
-      </c>
-      <c r="V10" s="13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Y10" s="13" t="n">
-        <v>19</v>
-      </c>
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
       <c r="AB10" s="14">
-        <f>V10*Y10</f>
+        <f>V10*Y10*1.0</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Grenade Launchers (M320A1)</t>
-        </is>
-      </c>
-      <c r="V11" s="13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Y11" s="13" t="n">
-        <v>4</v>
-      </c>
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
       <c r="AB11" s="14">
-        <f>V11*Y11</f>
+        <f>V11*Y11*1.0</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Thermal Sights (AN/PAS-13D)</t>
-        </is>
-      </c>
-      <c r="V12" s="13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Y12" s="13" t="n">
-        <v>4</v>
-      </c>
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
       <c r="AB12" s="14">
-        <f>V12*Y12</f>
+        <f>V12*Y12*1.0</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Other Sensitive Items (Optics, Accessories, Spares)</t>
-        </is>
-      </c>
-      <c r="V13" s="13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Y13" s="13" t="n">
-        <v>52</v>
-      </c>
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
       <c r="AB13" s="14">
-        <f>V13*Y13</f>
+        <f>V13*Y13*1.0</f>
         <v/>
       </c>
     </row>
@@ -3359,22 +5971,22 @@
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Total Sensitive Items, Total NSF</t>
+          <t>Subtotal NSF</t>
         </is>
       </c>
       <c r="AB15" s="14">
-        <f>SUM(AB8:AB13)</f>
+        <f>SUM(AB8:AF13)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Required GSF = ROUNDUP(Total NSF, 0)</t>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
         </is>
       </c>
       <c r="AB16" s="14">
-        <f>ROUNDUP(AB15,0)</f>
+        <f>AB15*1</f>
         <v/>
       </c>
     </row>
@@ -3404,13 +6016,13 @@
           <t>TOTAL REQUIREMENT:</t>
         </is>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="28">
         <f>AB16</f>
         <v/>
       </c>
       <c r="O37" s="18" t="inlineStr">
         <is>
-          <t>GSF</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="AB37" s="19" t="inlineStr"/>
@@ -3431,7 +6043,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>FC 2-000-05N 100 Series; version date 2026-02-11</t>
+          <t>FC 2-000-05N citation: TBD pending Series 800 (Utilities &amp; Ground; not yet supplied)</t>
         </is>
       </c>
       <c r="C41" s="21" t="n"/>
@@ -3444,7 +6056,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Source PDF: fc_2_000_05n_100series_02_11_2026.pdf</t>
+          <t>CCN 872 30 not in supplied Series 100/200 PDFs</t>
         </is>
       </c>
       <c r="C42" s="21" t="n"/>
@@ -3457,7 +6069,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Pages: [205]</t>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
         </is>
       </c>
       <c r="C43" s="21" t="n"/>
@@ -3467,21 +6079,8 @@
       <c r="G43" s="21" t="n"/>
       <c r="H43" s="22" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Table 14345-1 (Armory); loading driver: Installation Military Strength</t>
-        </is>
-      </c>
-      <c r="C44" s="21" t="n"/>
-      <c r="D44" s="21" t="n"/>
-      <c r="E44" s="21" t="n"/>
-      <c r="F44" s="21" t="n"/>
-      <c r="G44" s="21" t="n"/>
-      <c r="H44" s="22" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="56">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
@@ -3522,6 +6121,3056 @@
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
     <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>831 43</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>HAZ WASTE BLDG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 831 43  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>HAZ WASTE BLDG (Loading driver: Hazardous Waste Storage Building (SF); FAC 4423; 150-meter buffer from inhabited areas, ammo, or POL stores; short-term &lt;90 days vs long-term &gt;90 days; CLB-4 placeholder 400 SF for unit HAZMAT point)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="17">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 800 (Utilities &amp; Ground; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 831 43 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>831 41</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>HAZARD WSTE STOR &amp; TRANSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 831 41  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>HAZARD WSTE STOR &amp; TRANSFR (Loading driver: Hazardous Waste Storage and Transfer Facility (EA); FAC 8926; non-building structures; same 150-meter buffer rule; CLB-4 default 1 EA)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="17">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 800 (Utilities &amp; Ground; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 831 41 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>811 60</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>STANDBY GENERATOR PLANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 811 60  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>STANDBY GENERATOR PLANT (Loading driver: Standby Generator Plant (KW); FAC 8112; mission-essential standby power; CLB-4 placeholder 150 KW pending engineering load study)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="29">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 800 (Utilities &amp; Ground; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 811 60 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>880 10</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>FIRE ALARM COMM LINES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 880 10  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRE ALARM COMM LINES (Loading driver: Fire Alarm System (MI); FAC 1351; linear miles of fire-alarm wiring across CLB-4 compound; placeholder 1 MI pending site survey)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="30">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 800 (Utilities &amp; Ground; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 880 10 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>852 35</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>OTHER PAVED AREA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 852 35  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>OTHER PAVED AREA (Loading driver: Other Paved Areas Not in 100/400 Series (SY); FAC 8526; miscellaneous hardstand; CLB-4 placeholder 1000 SY)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="26">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 800 (Utilities &amp; Ground; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 852 35 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>852 40</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>MISC OPEN STRG/LAYDOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 852 40  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>MISC OPEN STRG/LAYDOWN (Loading driver: Misc Open Storage/Laydown Area Paved (SY); FAC 8526; PW open storage allowances per Table 85240-1; CLB-4 placeholder 2000 SY pending shop-type breakdown)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Primary loading row</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="Y9" s="13" t="inlineStr"/>
+      <c r="AB9" s="14">
+        <f>V9*Y9*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="AB10" s="14">
+        <f>V10*Y10*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="Y11" s="13" t="inlineStr"/>
+      <c r="AB11" s="14">
+        <f>V11*Y11*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="V12" s="13" t="inlineStr"/>
+      <c r="Y12" s="13" t="inlineStr"/>
+      <c r="AB12" s="14">
+        <f>V12*Y12*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="V13" s="13" t="inlineStr"/>
+      <c r="Y13" s="13" t="inlineStr"/>
+      <c r="AB13" s="14">
+        <f>V13*Y13*1.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AF13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net to Gross multiplier (NTG = 1.0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>AB15*1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="26">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSY</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N citation: TBD pending Series 800 (Utilities &amp; Ground; not yet supplied)</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>CCN 852 40 not in supplied Series 100/200 PDFs</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="AB13:AF13"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="A1:AF2"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="AB10:AF10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="AB37:AF37"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A4:U4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ROW</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>CCN</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>CCN Description</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>CCN 21451 Equipment Type</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>UIC</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>TAMCN Short</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>TAMCN</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Nomenclature</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>TAM Stat</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>U/I</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Rdy</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>Ind Qty</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>Org Qty</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Unit T/E</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>L, Ft</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>W, Ft</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>H, Ft</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>Volume Ea</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>Volume Total</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.5" top="0.75" bottom="0.5" header="0" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="84"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L_x000d_# DISTRIBUTION: DoD COMMUNITY ONLY</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.8164" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="9.18" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="9.18" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BASIC FACILITY REQUIREMENTS WORKSHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="30.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Installation:</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>MCB CAMP BUTLER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tenant:</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>CLB 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Installation UIC:</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>M67400</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tenant UIC:</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>M29030</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Planning Area: SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CCN:</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>143 45</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Nomenclature:</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>ARMORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SPACE REQUIREMENT ANALYSIS  ,  CCN 143 45  ,  FC 2-000-05N (Series 100, 11 Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="14.5" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Sensitive Item Category (Primary Items, all four companies)</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>GSF / Item</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Night Vision Devices (AN/PVS-14, AN/PVS-31D)</t>
+        </is>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y8" s="13" t="n">
+        <v>237</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>V8*Y8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Machine Guns (M240B, MK19 MOD 3)</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y9" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB9" s="14">
+        <f>V9*Y9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Rifles, Carbines, and Shotguns</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y10" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB10" s="14">
+        <f>V10*Y10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Grenade Launchers (M320A1)</t>
+        </is>
+      </c>
+      <c r="V11" s="13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB11" s="14">
+        <f>V11*Y11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Thermal Sights (AN/PAS-13D)</t>
+        </is>
+      </c>
+      <c r="V12" s="13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB12" s="14">
+        <f>V12*Y12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Other Sensitive Items (Optics, Accessories, Spares)</t>
+        </is>
+      </c>
+      <c r="V13" s="13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y13" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="AB13" s="14">
+        <f>V13*Y13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Total Sensitive Items, Total NSF</t>
+        </is>
+      </c>
+      <c r="AB15" s="14">
+        <f>SUM(AB8:AB13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Required GSF = ROUNDUP(Total NSF, 0)</t>
+        </is>
+      </c>
+      <c r="AB16" s="14">
+        <f>ROUNDUP(AB15,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL REQUIREMENT:</t>
+        </is>
+      </c>
+      <c r="H37" s="17">
+        <f>AB16</f>
+        <v/>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>GSF</t>
+        </is>
+      </c>
+      <c r="AB37" s="19" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N Citation (Apex Omega Sec.5.5)</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>FC 2-000-05N 100 Series; version date 2026-02-11</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Source PDF: fc_2_000_05n_100series_02_11_2026.pdf</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Pages: [205]</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Table 14345-1 (Armory); loading driver: Installation Military Strength</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    up to 2,000 | 576</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2,001 - 4,000 | 880</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    4,001 - 7,500 | 1,200</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="22" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    7,501 - 10,000 | 1,508</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="22" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Over 10,000 | Add 0.1 sq ft per person</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="62">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="AB15:AF15"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="A16:AA16"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="A12:U12"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="R3:AC3"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="AB11:AF11"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R5:AF5"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B48:H48"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="AB8:AF8"/>
@@ -4540,7 +10189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF43"/>
+  <dimension ref="A1:AF45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -4847,7 +10496,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>FC 2-000-05N citation: TBD pending Series 600 (Administrative; not yet supplied)</t>
+          <t>FC 2-000-05N 600 Series; version date 2023-03-02</t>
         </is>
       </c>
       <c r="C41" s="21" t="n"/>
@@ -4860,7 +10509,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>CCN 610 72 not in supplied Series 100/200 PDFs</t>
+          <t>Source PDF: fc_2_000_05n_600series_03_02_2023.pdf</t>
         </is>
       </c>
       <c r="C42" s="21" t="n"/>
@@ -4873,7 +10522,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Apex Omega rule 4: do not silently inherit CLB-4 values</t>
+          <t>Pages: [39]</t>
         </is>
       </c>
       <c r="C43" s="21" t="n"/>
@@ -4883,8 +10532,34 @@
       <c r="G43" s="21" t="n"/>
       <c r="H43" s="22" t="n"/>
     </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Engineering-study CCN per NAVFAC doctrine; 1 narrative section(s) captured</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  e.g. 61072-1: This category code is for a Fleet Marine Force (FMF) facility and provides</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="51">
     <mergeCell ref="A10:AF10"/>
     <mergeCell ref="Y20:AA20"/>
     <mergeCell ref="Y4:AF4"/>
@@ -4900,6 +10575,7 @@
     <mergeCell ref="AB14:AF14"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="V15:X15"/>
+    <mergeCell ref="B45:H45"/>
     <mergeCell ref="A11:AF11"/>
     <mergeCell ref="Y16:AA16"/>
     <mergeCell ref="AE3:AF3"/>
@@ -4931,6 +10607,7 @@
     <mergeCell ref="A1:AF2"/>
     <mergeCell ref="Y15:AA15"/>
     <mergeCell ref="A8:AF8"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="V20:X20"/>
     <mergeCell ref="AB37:AF37"/>
     <mergeCell ref="M4:Q4"/>
@@ -4955,7 +10632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF46"/>
+  <dimension ref="A1:AF61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.8164" customWidth="1" min="1" max="1"/>
@@ -5292,7 +10969,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  page_190_table_2 (); loading driver: TBD</t>
+          <t xml:space="preserve">    Non-mechanized CESE and SABAR (ex: Small (&lt;10FT) Fuel Water SIXCON, Motors, Pumps, A 19 168 1.50 Generators, TRICONS)</t>
         </is>
       </c>
       <c r="C45" s="21" t="n"/>
@@ -5305,7 +10982,7 @@
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  page_190_table_3 (); loading driver: TBD</t>
+          <t xml:space="preserve">    Vehicles and non-mechanized CESE and Medium (10FT- SABAR (ex: Passenger Vehicles, B 32 288 1.75 20FT) HMMWV, Light Plant, Fork Lifts, Small Zodiac Boats)</t>
         </is>
       </c>
       <c r="C46" s="21" t="n"/>
@@ -5315,8 +10992,203 @@
       <c r="G46" s="21" t="n"/>
       <c r="H46" s="22" t="n"/>
     </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Large CESE and SABAR (ex: MTVR, Fuel Large (20FT-30FT) C 46 408 1.75 Trucks, Boats &lt; 30FT)</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="22" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Extra Large CESE and SABAR (ex: Boats Extra Large (30FT- &gt; 30FT, Scrapers, Water Well, Semi D 59 528 2.00 40FT) Trailers)</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="22" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Extra Large CESE and SABAR (ex: Boats Extra Large (40FT- &gt; 40FT, Scrapers, Water Well, Semi E 72 648 2.00 50FT) Trailers)</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="22" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Extra Large (50FT- Extra Large CESE and SABAR (ex: Boats F 86 768 2.25 60FT) &gt; 50 FT, Semi Trailers, lowboy 55T)</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="21" t="n"/>
+      <c r="H50" s="22" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Extra Large CESE and SABAR (ex: 11M Extra Large (60FT- Rib with Prime Mover; 40PB with Prime G 99 888 2.25 70FT) Mover)</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="22" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_190_table_2 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="22" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  page_190_table_3 (); loading driver: TBD</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="22" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1A | 5</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="22" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    A | 10</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="21" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="22" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1B | 15</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="21" t="n"/>
+      <c r="E56" s="21" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="22" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    B | 20</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="21" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="22" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    C | 30</t>
+        </is>
+      </c>
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="21" t="n"/>
+      <c r="E58" s="21" t="n"/>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="21" t="n"/>
+      <c r="H58" s="22" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    D | 40</t>
+        </is>
+      </c>
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="21" t="n"/>
+      <c r="E59" s="21" t="n"/>
+      <c r="F59" s="21" t="n"/>
+      <c r="G59" s="21" t="n"/>
+      <c r="H59" s="22" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    E | 50</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="21" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="22" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    F | 60</t>
+        </is>
+      </c>
+      <c r="C61" s="21" t="n"/>
+      <c r="D61" s="21" t="n"/>
+      <c r="E61" s="21" t="n"/>
+      <c r="F61" s="21" t="n"/>
+      <c r="G61" s="21" t="n"/>
+      <c r="H61" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="74">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="Y4:AF4"/>
@@ -5325,28 +11197,38 @@
     <mergeCell ref="A7:U7"/>
     <mergeCell ref="AB15:AF15"/>
     <mergeCell ref="V9:X9"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="A16:AA16"/>
     <mergeCell ref="H37:K37"/>
+    <mergeCell ref="B55:H55"/>
     <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="B51:H51"/>
     <mergeCell ref="Y7:AA7"/>
     <mergeCell ref="B45:H45"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="A12:U12"/>
     <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B50:H50"/>
     <mergeCell ref="B41:H41"/>
     <mergeCell ref="R3:AC3"/>
     <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="A6:AF6"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="AB16:AF16"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B54:H54"/>
     <mergeCell ref="Y12:AA12"/>
     <mergeCell ref="AB9:AF9"/>
+    <mergeCell ref="B59:H59"/>
     <mergeCell ref="V7:X7"/>
     <mergeCell ref="A8:U8"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="B46:H46"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="AB12:AF12"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B52:H52"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="AB11:AF11"/>
     <mergeCell ref="B43:H43"/>
@@ -5359,16 +11241,21 @@
     <mergeCell ref="R5:AF5"/>
     <mergeCell ref="A13:U13"/>
     <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B48:H48"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A9:U9"/>
+    <mergeCell ref="B60:H60"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B61:H61"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="AB13:AF13"/>
     <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="B57:H57"/>
     <mergeCell ref="A15:AA15"/>
     <mergeCell ref="A1:AF2"/>
     <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B53:H53"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="A11:U11"/>
